--- a/data/xlsx/sbce_config_kvm_ems+sbce_template.xlsx
+++ b/data/xlsx/sbce_config_kvm_ems+sbce_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="123">
   <si>
     <t xml:space="preserve">platform_type</t>
   </si>
@@ -110,6 +110,9 @@
   </si>
   <si>
     <t xml:space="preserve">appname</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sbcemsapp</t>
   </si>
   <si>
     <t xml:space="preserve">Appliance Name</t>
@@ -999,408 +1002,408 @@
         <v>29</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>64</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(B9, ".", B20)</f>
         <v>sbcems.lab.local</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/data/xlsx/sbce_config_kvm_ems+sbce_template.xlsx
+++ b/data/xlsx/sbce_config_kvm_ems+sbce_template.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="SBCEMS" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="SBCEMS" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="124">
   <si>
     <t xml:space="preserve">platform_type</t>
   </si>
@@ -139,7 +139,7 @@
     <t xml:space="preserve">ip0</t>
   </si>
   <si>
-    <t xml:space="preserve">192.168.122.180</t>
+    <t xml:space="preserve">10.10.10.10</t>
   </si>
   <si>
     <t xml:space="preserve">Management IPv4 Address: (*) - The IPv4 address for the management interface.</t>
@@ -157,6 +157,9 @@
     <t xml:space="preserve">gateway</t>
   </si>
   <si>
+    <t xml:space="preserve">10.10.10.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Default gateway: (*) - The IPv4 gateway for the management interface.</t>
   </si>
   <si>
@@ -307,7 +310,7 @@
     <t xml:space="preserve">M1</t>
   </si>
   <si>
-    <t xml:space="preserve">virbr0</t>
+    <t xml:space="preserve">lab</t>
   </si>
   <si>
     <t xml:space="preserve">M1 NIC Port-group / Bridge name</t>
@@ -385,7 +388,7 @@
     <t xml:space="preserve">sig_ip</t>
   </si>
   <si>
-    <t xml:space="preserve">192.168.122.181</t>
+    <t xml:space="preserve">10.10.10.18</t>
   </si>
   <si>
     <t xml:space="preserve">SIP data interface IP address</t>
@@ -395,13 +398,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
   <fonts count="4">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
@@ -464,7 +468,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -481,6 +485,10 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -494,147 +502,147 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -702,185 +710,13 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0e2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="e8e8e8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="e97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196b24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0f9ed5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="a02b93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4ea72e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607d"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="70.22"/>
@@ -1057,353 +893,353 @@
         <v>44</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>64</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B21" s="1" t="str">
+        <v>56</v>
+      </c>
+      <c r="B21" s="4" t="str">
         <f aca="false">_xlfn.CONCAT(B9, ".", B20)</f>
         <v>sbcems.lab.local</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1575,7 +1411,7 @@
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>

--- a/data/xlsx/sbce_config_kvm_ems+sbce_template.xlsx
+++ b/data/xlsx/sbce_config_kvm_ems+sbce_template.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="SBCEMS" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="SBCEMS" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="122">
   <si>
     <t xml:space="preserve">platform_type</t>
   </si>
@@ -310,9 +310,6 @@
     <t xml:space="preserve">M1</t>
   </si>
   <si>
-    <t xml:space="preserve">lab</t>
-  </si>
-  <si>
     <t xml:space="preserve">M1 NIC Port-group / Bridge name</t>
   </si>
   <si>
@@ -386,9 +383,6 @@
   </si>
   <si>
     <t xml:space="preserve">sig_ip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.10.10.18</t>
   </si>
   <si>
     <t xml:space="preserve">SIP data interface IP address</t>
@@ -398,9 +392,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -468,7 +461,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -483,10 +476,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -710,13 +699,119 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.62109375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="70.22"/>
@@ -941,7 +1036,7 @@
       <c r="A21" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="4" t="str">
+      <c r="B21" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(B9, ".", B20)</f>
         <v>sbcems.lab.local</v>
       </c>
@@ -1110,136 +1205,136 @@
         <v>95</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C38" s="1" t="s">
+    </row>
+    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+      <c r="B39" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C39" s="1" t="s">
+    </row>
+    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+      <c r="B40" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C40" s="1" t="s">
+    </row>
+    <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+      <c r="B41" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C41" s="1" t="s">
+    </row>
+    <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+      <c r="B42" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C48" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+      <c r="B49" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1411,7 +1506,7 @@
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>

--- a/data/xlsx/sbce_config_kvm_ems+sbce_template.xlsx
+++ b/data/xlsx/sbce_config_kvm_ems+sbce_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="124">
   <si>
     <t xml:space="preserve">platform_type</t>
   </si>
@@ -379,10 +379,16 @@
     <t xml:space="preserve">sig_gw</t>
   </si>
   <si>
+    <t xml:space="preserve">10.10.11.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">SIP data interface default gateway</t>
   </si>
   <si>
     <t xml:space="preserve">sig_ip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.10.11.10</t>
   </si>
   <si>
     <t xml:space="preserve">SIP data interface IP address</t>
@@ -1320,21 +1326,21 @@
         <v>118</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
